--- a/store_inventory_template.xlsx
+++ b/store_inventory_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="460">
   <si>
     <t>category_id</t>
   </si>
@@ -29,115 +29,127 @@
     <t>description</t>
   </si>
   <si>
+    <t>brand</t>
+  </si>
+  <si>
     <t>seo_title</t>
   </si>
   <si>
-    <t>brand</t>
-  </si>
-  <si>
     <t>seo_description</t>
   </si>
   <si>
     <t>category_name</t>
   </si>
   <si>
+    <t>varient_label</t>
+  </si>
+  <si>
     <t>cat_001</t>
   </si>
   <si>
-    <t>varient_label</t>
+    <t>original_price</t>
   </si>
   <si>
     <t>Kids Cycle</t>
   </si>
   <si>
-    <t>original_price</t>
+    <t>discounted_price</t>
   </si>
   <si>
     <t>kids-cycle</t>
   </si>
   <si>
-    <t>discounted_price</t>
+    <t>discount_percent</t>
   </si>
   <si>
     <t>Kids Cycle available at KTR Cycle World, Tirunelveli.</t>
   </si>
   <si>
-    <t>discount_percent</t>
+    <t>stock</t>
   </si>
   <si>
     <t>Kids Cycle | KTR Cycle World</t>
   </si>
   <si>
-    <t>stock</t>
+    <t>featured</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
   <si>
     <t>cat_002</t>
   </si>
   <si>
-    <t>featured</t>
+    <t>color</t>
   </si>
   <si>
     <t>Adult Cycle</t>
   </si>
   <si>
-    <t>location</t>
+    <t>age_group</t>
   </si>
   <si>
     <t>adult-cycle</t>
   </si>
   <si>
-    <t>color</t>
+    <t>tags</t>
   </si>
   <si>
     <t>Adult Cycle available at KTR Cycle World, Tirunelveli.</t>
   </si>
   <si>
-    <t>age_group</t>
-  </si>
-  <si>
     <t>Adult Cycle | KTR Cycle World</t>
   </si>
   <si>
-    <t>tags</t>
+    <t>short_description</t>
+  </si>
+  <si>
+    <t>long_description</t>
   </si>
   <si>
     <t>cat_003</t>
   </si>
   <si>
-    <t>short_description</t>
-  </si>
-  <si>
     <t>Geared Cycle</t>
   </si>
   <si>
+    <t>specifications</t>
+  </si>
+  <si>
+    <t>features</t>
+  </si>
+  <si>
     <t>geared-cycle</t>
   </si>
   <si>
-    <t>long_description</t>
-  </si>
-  <si>
     <t>Geared Cycle available at KTR Cycle World, Tirunelveli.</t>
   </si>
   <si>
     <t>Geared Cycle | KTR Cycle World</t>
   </si>
   <si>
-    <t>specifications</t>
-  </si>
-  <si>
-    <t>features</t>
+    <t>images</t>
+  </si>
+  <si>
+    <t>prod_001</t>
   </si>
   <si>
     <t>cat_004</t>
   </si>
   <si>
+    <t>Alpha Bombay 26 VB</t>
+  </si>
+  <si>
     <t>Girls Cycle</t>
   </si>
   <si>
+    <t>alpha-bombay-26-vb</t>
+  </si>
+  <si>
     <t>girls-cycle</t>
   </si>
   <si>
-    <t>images</t>
+    <t>ALPHA</t>
   </si>
   <si>
     <t>Girls Cycle available at KTR Cycle World, Tirunelveli.</t>
@@ -146,69 +158,60 @@
     <t>Girls Cycle | KTR Cycle World</t>
   </si>
   <si>
-    <t>prod_001</t>
-  </si>
-  <si>
-    <t>Alpha Bombay 26 VB</t>
-  </si>
-  <si>
     <t>cat_005</t>
   </si>
   <si>
-    <t>alpha-bombay-26-vb</t>
-  </si>
-  <si>
     <t>Electric Cycle</t>
   </si>
   <si>
-    <t>ALPHA</t>
+    <t>FALSE</t>
   </si>
   <si>
     <t>electric-cycle</t>
   </si>
   <si>
+    <t>Tirunelveli</t>
+  </si>
+  <si>
     <t>Electric Cycle available at KTR Cycle World, Tirunelveli.</t>
   </si>
   <si>
+    <t>15+ Years</t>
+  </si>
+  <si>
     <t>Electric Cycle | KTR Cycle World</t>
   </si>
   <si>
+    <t>Alpha Bombay 26 VB - KTR Cycle World</t>
+  </si>
+  <si>
     <t>cat_006</t>
   </si>
   <si>
+    <t>/images/products/prod_001_1.jpg</t>
+  </si>
+  <si>
     <t>Offer cycle</t>
   </si>
   <si>
+    <t>prod_002</t>
+  </si>
+  <si>
     <t>offer-cycle</t>
   </si>
   <si>
+    <t>SKYWALK 20"</t>
+  </si>
+  <si>
     <t>Offer cycle available at KTR Cycle World, Tirunelveli.</t>
   </si>
   <si>
+    <t>skywalk-20</t>
+  </si>
+  <si>
     <t>Offer cycle | KTR Cycle World</t>
   </si>
   <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>Tirunelveli</t>
-  </si>
-  <si>
-    <t>Alpha Bombay 26 VB - KTR Cycle World</t>
-  </si>
-  <si>
-    <t>/images/products/prod_001_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_002</t>
-  </si>
-  <si>
-    <t>SKYWALK 20"</t>
-  </si>
-  <si>
-    <t>skywalk-20</t>
-  </si>
-  <si>
     <t>TORONTO</t>
   </si>
   <si>
@@ -218,6 +221,9 @@
     <t>TRUE</t>
   </si>
   <si>
+    <t>8-12 Years</t>
+  </si>
+  <si>
     <t>KIDS CYCLE</t>
   </si>
   <si>
@@ -275,7 +281,7 @@
     <t>Alpha cairo 24 FSDD</t>
   </si>
   <si>
-    <t xml:space="preserve">91 Alpha Cairo 24T D2TX 3.0 </t>
+    <t>12-15 Years</t>
   </si>
   <si>
     <t>91 Alpha Cairo 24T D2TX 3.0 - KTR Cycle World</t>
@@ -452,6 +458,9 @@
     <t>hercules</t>
   </si>
   <si>
+    <t>2-5 Years</t>
+  </si>
+  <si>
     <t>kids cycle for under 5 years</t>
   </si>
   <si>
@@ -488,6 +497,9 @@
     <t>bsa-champ-16t</t>
   </si>
   <si>
+    <t>5-8 Years</t>
+  </si>
+  <si>
     <t>kids cycle under 8 years</t>
   </si>
   <si>
@@ -944,9 +956,6 @@
     <t>hercules-rift-ic-fx-dd-24t</t>
   </si>
   <si>
-    <t xml:space="preserve">Hercules Rift IC FX DD 24T </t>
-  </si>
-  <si>
     <t>Hercules Rift IC FX DD 24T - KTR Cycle World</t>
   </si>
   <si>
@@ -962,9 +971,6 @@
     <t>hercules-rift-ic-fx-dd-26t</t>
   </si>
   <si>
-    <t xml:space="preserve">Hercules Rift IC FX DD 26T </t>
-  </si>
-  <si>
     <t>Hercules Rift IC FX DD 26T - KTR Cycle World</t>
   </si>
   <si>
@@ -980,9 +986,6 @@
     <t>hercules-rift-ic-rf-vb-24t</t>
   </si>
   <si>
-    <t xml:space="preserve">Hercules Rift IC RF VB 24T </t>
-  </si>
-  <si>
     <t>Hercules Rift IC RF VB 24T - KTR Cycle World</t>
   </si>
   <si>
@@ -1103,9 +1106,6 @@
     <t>SUNCROSS</t>
   </si>
   <si>
-    <t xml:space="preserve">HURRICANE 26T </t>
-  </si>
-  <si>
     <t>HURRICANE 26T - KTR Cycle World</t>
   </si>
   <si>
@@ -1244,9 +1244,6 @@
     <t>navarro-one</t>
   </si>
   <si>
-    <t xml:space="preserve">NAVARRO ONE </t>
-  </si>
-  <si>
     <t>NAVARRO ONE - KTR Cycle World</t>
   </si>
   <si>
@@ -1382,7 +1379,7 @@
     <t>MadRock 27.5T</t>
   </si>
   <si>
-    <t>madrock-27.5t</t>
+    <t>madrock-275t</t>
   </si>
   <si>
     <t>GEAR,ADULT</t>
@@ -1401,7 +1398,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -1412,17 +1409,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FF9E9E9E"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FFE8E8E8"/>
-      <name val="Sans-serif"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1439,18 +1425,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1687,8 +1666,7 @@
     <col customWidth="1" min="18" max="21" width="45.78"/>
     <col customWidth="1" min="22" max="22" width="35.78"/>
     <col customWidth="1" min="23" max="23" width="45.78"/>
-    <col customWidth="1" min="24" max="24" width="79.22"/>
-    <col customWidth="1" min="25" max="25" width="20.0"/>
+    <col customWidth="1" min="24" max="24" width="35.78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1702,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -1711,81 +1689,81 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="Q1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1">
         <v>7200.0</v>
@@ -1800,45 +1778,48 @@
         <v>1.0</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="1">
         <v>11200.0</v>
@@ -1853,51 +1834,54 @@
         <v>3.0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H4" s="1">
         <v>11200.0</v>
@@ -1912,51 +1896,54 @@
         <v>3.0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="H5" s="1">
         <v>6400.0</v>
@@ -1971,51 +1958,54 @@
         <v>3.0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H6" s="1">
         <v>10200.0</v>
@@ -2030,45 +2020,48 @@
         <v>1.0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="H7" s="1">
         <v>10400.0</v>
@@ -2083,51 +2076,54 @@
         <v>6.0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H8" s="1">
         <v>7800.0</v>
@@ -2142,48 +2138,51 @@
         <v>1.0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H9" s="1">
         <v>8500.0</v>
@@ -2198,48 +2197,51 @@
         <v>1.0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="W9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="W9" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="X9" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="H10" s="1">
         <v>7600.0</v>
@@ -2254,48 +2256,51 @@
         <v>3.0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H11" s="1">
         <v>13500.0</v>
@@ -2310,51 +2315,54 @@
         <v>2.0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H12" s="1">
         <v>7900.0</v>
@@ -2369,51 +2377,54 @@
         <v>2.0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H13" s="1">
         <v>7800.0</v>
@@ -2428,48 +2439,51 @@
         <v>4.0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="W13" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="X13" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1">
         <v>0.0</v>
@@ -2484,51 +2498,54 @@
         <v>0.0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="H15" s="1">
         <v>4400.0</v>
@@ -2543,51 +2560,54 @@
         <v>3.0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H16" s="1">
         <v>4500.0</v>
@@ -2602,51 +2622,54 @@
         <v>4.0</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H17" s="1">
         <v>4900.0</v>
@@ -2661,51 +2684,54 @@
         <v>3.0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H18" s="1">
         <v>5450.0</v>
@@ -2720,51 +2746,54 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H19" s="1">
         <v>5300.0</v>
@@ -2779,48 +2808,51 @@
         <v>3.0</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H20" s="1">
         <v>8400.0</v>
@@ -2835,51 +2867,54 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H21" s="1">
         <v>12500.0</v>
@@ -2894,48 +2929,51 @@
         <v>2.0</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="V21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="W21" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="X21" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H22" s="1">
         <v>38000.0</v>
@@ -2950,54 +2988,57 @@
         <v>3.0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H23" s="1">
         <v>24000.0</v>
@@ -3012,51 +3053,54 @@
         <v>3.0</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H24" s="1">
         <v>12500.0</v>
@@ -3071,42 +3115,45 @@
         <v>1.0</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H25" s="1">
         <v>14175.0</v>
@@ -3121,51 +3168,54 @@
         <v>1.0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H26" s="1">
         <v>31000.0</v>
@@ -3180,51 +3230,54 @@
         <v>3.0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H27" s="1">
         <v>9999.0</v>
@@ -3239,48 +3292,51 @@
         <v>1.0</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H28" s="1">
         <v>20400.0</v>
@@ -3295,48 +3351,51 @@
         <v>2.0</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H29" s="1">
         <v>19000.0</v>
@@ -3351,51 +3410,54 @@
         <v>3.0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H30" s="1">
         <v>29900.0</v>
@@ -3410,54 +3472,57 @@
         <v>3.0</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H31" s="1">
         <v>5200.0</v>
@@ -3472,48 +3537,51 @@
         <v>5.0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H32" s="1">
         <v>7200.0</v>
@@ -3528,48 +3596,51 @@
         <v>3.0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H33" s="1">
         <v>27500.0</v>
@@ -3584,54 +3655,57 @@
         <v>3.0</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H34" s="1">
         <v>13500.0</v>
@@ -3646,48 +3720,51 @@
         <v>2.0</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H35" s="1">
         <v>6800.0</v>
@@ -3702,48 +3779,51 @@
         <v>3.0</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H36" s="1">
         <v>3500.0</v>
@@ -3758,48 +3838,51 @@
         <v>3.0</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H37" s="1">
         <v>4200.0</v>
@@ -3814,48 +3897,51 @@
         <v>3.0</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H38" s="1">
         <v>3600.0</v>
@@ -3870,48 +3956,51 @@
         <v>3.0</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H39" s="1">
         <v>8200.0</v>
@@ -3926,48 +4015,51 @@
         <v>3.0</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H40" s="1">
         <v>8100.0</v>
@@ -3982,48 +4074,51 @@
         <v>3.0</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H41" s="1">
         <v>8200.0</v>
@@ -4038,48 +4133,51 @@
         <v>3.0</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="V41" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="W41" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="W41" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="X41" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H42" s="1">
         <v>6900.0</v>
@@ -4094,48 +4192,51 @@
         <v>3.0</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>322</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>322</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H43" s="1">
         <v>13000.0</v>
@@ -4150,48 +4251,51 @@
         <v>3.0</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H44" s="1">
         <v>22000.0</v>
@@ -4206,54 +4310,57 @@
         <v>3.0</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R44" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="W44" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="S44" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="W44" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="X44" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H45" s="1">
         <v>30400.0</v>
@@ -4268,48 +4375,51 @@
         <v>3.0</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="H46" s="1">
         <v>32000.0</v>
@@ -4324,51 +4434,54 @@
         <v>0.0</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="V46" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="W46" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="W46" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="X46" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H47" s="1">
         <v>5900.0</v>
@@ -4383,48 +4496,51 @@
         <v>3.0</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H48" s="1">
         <v>7800.0</v>
@@ -4439,48 +4555,51 @@
         <v>3.0</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H49" s="1">
         <v>14200.0</v>
@@ -4495,22 +4614,25 @@
         <v>3.0</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="V49" s="1" t="s">
         <v>364</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="X49" s="1" t="s">
         <v>365</v>
@@ -4527,16 +4649,16 @@
         <v>368</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H50" s="1">
         <v>13995.0</v>
@@ -4551,13 +4673,16 @@
         <v>3.0</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S50" s="1" t="s">
         <v>367</v>
@@ -4583,16 +4708,16 @@
         <v>373</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H51" s="1">
         <v>17000.0</v>
@@ -4607,13 +4732,16 @@
         <v>3.0</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>372</v>
@@ -4639,16 +4767,16 @@
         <v>378</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H52" s="1">
         <v>4700.0</v>
@@ -4663,13 +4791,16 @@
         <v>3.0</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>377</v>
@@ -4695,16 +4826,16 @@
         <v>383</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H53" s="1">
         <v>20200.0</v>
@@ -4719,13 +4850,16 @@
         <v>3.0</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>382</v>
@@ -4754,10 +4888,10 @@
         <v>389</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>389</v>
@@ -4775,13 +4909,16 @@
         <v>3.0</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>387</v>
@@ -4810,10 +4947,10 @@
         <v>395</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>395</v>
@@ -4831,13 +4968,16 @@
         <v>3.0</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>393</v>
@@ -4866,10 +5006,10 @@
         <v>401</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>399</v>
@@ -4887,10 +5027,13 @@
         <v>0.0</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>402</v>
@@ -4925,16 +5068,16 @@
         <v>409</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H57" s="1">
         <v>13000.0</v>
@@ -4949,48 +5092,51 @@
         <v>3.0</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S57" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="V57" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="V57" s="1" t="s">
+      <c r="W57" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="X57" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="W57" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="X57" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="D58" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H58" s="1">
         <v>8500.0</v>
@@ -5005,48 +5151,51 @@
         <v>1.0</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V58" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="W58" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="X58" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="W58" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="X58" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="H59" s="1">
         <v>7300.0</v>
@@ -5061,48 +5210,51 @@
         <v>1.0</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="V59" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="X59" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="W59" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="X59" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="D60" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H60" s="1">
         <v>8200.0</v>
@@ -5117,48 +5269,51 @@
         <v>1.0</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="V60" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="X60" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="W60" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="X60" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="D61" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H61" s="1">
         <v>17200.0</v>
@@ -5173,48 +5328,51 @@
         <v>1.0</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="V61" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="X61" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="W61" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="X61" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="D62" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H62" s="1">
         <v>12200.0</v>
@@ -5229,48 +5387,51 @@
         <v>3.0</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V62" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="X62" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="W62" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="X62" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H63" s="1">
         <v>13100.0</v>
@@ -5285,48 +5446,51 @@
         <v>1.0</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="V63" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="X63" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="W63" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="X63" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H64" s="1">
         <v>12500.0</v>
@@ -5341,48 +5505,51 @@
         <v>1.0</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="V64" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="X64" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="W64" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="X64" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>401</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H65" s="1">
         <v>73000.0</v>
@@ -5397,10 +5564,13 @@
         <v>0.0</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>402</v>
@@ -5415,74 +5585,78 @@
         <v>404</v>
       </c>
       <c r="V65" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>403</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H66" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>16.67</v>
+      </c>
+      <c r="K66" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P66" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H66" s="2">
-        <v>30000.0</v>
-      </c>
-      <c r="I66" s="2">
-        <v>25000.0</v>
-      </c>
-      <c r="K66" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L66" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P66" s="2" t="s">
+      <c r="R66" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="S66" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="S66" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="V66" s="2" t="s">
+      <c r="W66" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="X66" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="W66" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="X66" s="2" t="s">
-        <v>460</v>
-      </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="R67" s="4"/>
-    </row>
+    <row r="67" ht="15.75" customHeight="1"/>
     <row r="68" ht="15.75" customHeight="1"/>
     <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
@@ -6446,7 +6620,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6454,122 +6628,122 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/store_inventory_template.xlsx
+++ b/store_inventory_template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:L52"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -410,7 +410,8 @@
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="65.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
+    <col min="11" max="11" width="80.83203125" customWidth="1"/>
+    <col min="12" max="12" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,6 +446,9 @@
         <v>description</v>
       </c>
       <c r="K1" t="str">
+        <v>specifications</v>
+      </c>
+      <c r="L1" t="str">
         <v>images</v>
       </c>
     </row>
@@ -480,6 +484,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K2" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L2" t="str">
         <v>/images/products/prod_001_1_1cBHXAZIQpKTodzPqbos1Ngp1sV-MFDwC.jpg,/images/products/prod_001_2_1Iv7MRj7lY8BSTD19GLEGM0ZcK6zuQYd1.jpg</v>
       </c>
     </row>
@@ -515,6 +522,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K3" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L3" t="str">
         <v>/images/products/prod_002_1_1UMFTn5JP9w2FFi4KL6l-8diVc5gUkx-Z.jpg</v>
       </c>
     </row>
@@ -550,6 +560,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K4" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L4" t="str">
         <v>/images/products/prod_005_1.jpg</v>
       </c>
     </row>
@@ -585,6 +598,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K5" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L5" t="str">
         <v>/images/products/prod_006_1.jpg</v>
       </c>
     </row>
@@ -620,6 +636,9 @@
         <v>Elegant and comfortable girls cycle featuring low step-through frame, comfortable upright geometry, rear carrier, and smooth brake controls.</v>
       </c>
       <c r="K6" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L6" t="str">
         <v>/images/products/prod_009_1.jpg</v>
       </c>
     </row>
@@ -655,6 +674,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K7" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L7" t="str">
         <v>/images/products/prod_011_1.jpg,/images/products/prod_011_2.jpg,/images/products/prod_011_3_1mab42s_Mf84sxHNRZbtB6q6yn-2m0tMB.jpg</v>
       </c>
     </row>
@@ -690,6 +712,9 @@
         <v>Elegant and comfortable girls cycle featuring low step-through frame, comfortable upright geometry, rear carrier, and smooth brake controls.</v>
       </c>
       <c r="K8" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L8" t="str">
         <v>/images/products/prod_012_1.jpg,/images/products/prod_012_2.jpg,/images/products/prod_012_3.jpg</v>
       </c>
     </row>
@@ -725,6 +750,9 @@
         <v>Avon Yama 26T FAT is a rugged fat-tire bicycle featuring extra-wide 4.0" all-terrain tires, heavy-duty suspension, and 21-speed gears for ultimate traction and off-road dominance.</v>
       </c>
       <c r="K9" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Multi-Speed Gear System | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</v>
+      </c>
+      <c r="L9" t="str">
         <v>/images/products/prod_013_1.jpg,/images/products/prod_013_2.jpg,/images/products/prod_013_3.jpg</v>
       </c>
     </row>
@@ -760,6 +788,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (2-5 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K10" t="str">
+        <v>Wheel Size: 12 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L10" t="str">
         <v>/images/products/prod_014_1.jpg</v>
       </c>
     </row>
@@ -795,6 +826,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (2-5 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K11" t="str">
+        <v>Wheel Size: 14 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L11" t="str">
         <v>/images/products/prod_015_1.jpg</v>
       </c>
     </row>
@@ -830,6 +864,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (5-8 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K12" t="str">
+        <v>Wheel Size: 16 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 5-8 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L12" t="str">
         <v>/images/products/prod_016_1.jpg</v>
       </c>
     </row>
@@ -865,6 +902,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K13" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L13" t="str">
         <v>/images/products/prod_017_1.jpg</v>
       </c>
     </row>
@@ -900,6 +940,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K14" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Caliper Brakes with Soft-Grip Rubber Pads | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L14" t="str">
         <v>/images/products/prod_018_1.jpg</v>
       </c>
     </row>
@@ -935,6 +978,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K15" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L15" t="str">
         <v>/images/products/prod_019_1.jpg</v>
       </c>
     </row>
@@ -970,6 +1016,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K16" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L16" t="str">
         <v>/images/products/prod_020_1.jpg</v>
       </c>
     </row>
@@ -1005,6 +1054,9 @@
         <v>Montra Hypno PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K17" t="str">
+        <v>Wheel Size: 27.5 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L17" t="str">
         <v>/images/products/prod_021_1.jpg,/images/products/prod_021_2.jpg</v>
       </c>
     </row>
@@ -1040,6 +1092,9 @@
         <v>BSA Viona 26T is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K18" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L18" t="str">
         <v>/images/products/prod_022_1.jpg,/images/products/prod_022_2.jpg,/images/products/prod_022_3.jpg</v>
       </c>
     </row>
@@ -1075,6 +1130,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K19" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L19" t="str">
         <v>/images/products/prod_024_1.jpg,/images/products/prod_024_2.jpg,/images/products/prod_024_3.jpg</v>
       </c>
     </row>
@@ -1110,6 +1168,9 @@
         <v>Maeve 26T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K20" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L20" t="str">
         <v>/images/products/prod_025_1.jpg</v>
       </c>
     </row>
@@ -1145,6 +1206,9 @@
         <v>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</v>
       </c>
       <c r="K21" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L21" t="str">
         <v>/images/products/prod_027_1.jpg</v>
       </c>
     </row>
@@ -1180,6 +1244,9 @@
         <v>Hercules Brute 27T FSDD EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K22" t="str">
+        <v>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L22" t="str">
         <v>/images/products/prod_029_1.jpg</v>
       </c>
     </row>
@@ -1215,6 +1282,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K23" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L23" t="str">
         <v>/images/products/prod_030_1.jpg</v>
       </c>
     </row>
@@ -1250,6 +1320,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K24" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L24" t="str">
         <v>/images/products/prod_031_1.jpg</v>
       </c>
     </row>
@@ -1285,6 +1358,9 @@
         <v>Hercules Hardstyle PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K25" t="str">
+        <v>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L25" t="str">
         <v>/images/products/prod_032_1.jpg</v>
       </c>
     </row>
@@ -1320,6 +1396,9 @@
         <v>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</v>
       </c>
       <c r="K26" t="str">
+        <v>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L26" t="str">
         <v>/images/products/prod_033_1.jpg</v>
       </c>
     </row>
@@ -1355,6 +1434,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K27" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L27" t="str">
         <v>/images/products/prod_034_1.jpg</v>
       </c>
     </row>
@@ -1390,6 +1472,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (2-5 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K28" t="str">
+        <v>Wheel Size: 14 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L28" t="str">
         <v>/images/products/prod_035_1.jpg</v>
       </c>
     </row>
@@ -1425,6 +1510,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K29" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L29" t="str">
         <v>/images/products/prod_036_1.jpg</v>
       </c>
     </row>
@@ -1460,6 +1548,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (5-8 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K30" t="str">
+        <v>Wheel Size: 16 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 5-8 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L30" t="str">
         <v>/images/products/prod_037_1.jpg</v>
       </c>
     </row>
@@ -1495,6 +1586,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K31" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L31" t="str">
         <v>/images/products/prod_030_1_1qVziSjWYCGFf8R3oIKmAzKjvcNZu0KnG.jpg</v>
       </c>
     </row>
@@ -1530,6 +1624,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K32" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L32" t="str">
         <v>/images/products/prod_040_1_1g-pYq_s7n50qf5m2eJN9l5r_v4edU99Z.jpg</v>
       </c>
     </row>
@@ -1565,6 +1662,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K33" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L33" t="str">
         <v>/images/products/prod_032_1_1rYYvmQpehc6qpBH7YOz0jT_aI1uTEsOQ.jpg,/images/products/prod_032_2_1qSfD9okHkQmY7E8OFcqcUlRURRiPHH8D.jpg</v>
       </c>
     </row>
@@ -1600,6 +1700,9 @@
         <v>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</v>
       </c>
       <c r="K34" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L34" t="str">
         <v>/images/products/prod_042_1_1VGfMRvQitXL1aQYdeM933R_pw4jiJXss.jpg</v>
       </c>
     </row>
@@ -1635,6 +1738,9 @@
         <v>Hercules Shurveer EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K35" t="str">
+        <v>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L35" t="str">
         <v>/images/products/prod_043_1_18abkEN_bcgrKPFHkF5ttxu6aWRIccoNj.jpg</v>
       </c>
     </row>
@@ -1670,6 +1776,9 @@
         <v>Raleigh E-surge S/s Eco is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K36" t="str">
+        <v>Wheel Size: Standard Size | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L36" t="str">
         <v>/images/products/prod_044_1.jpg</v>
       </c>
     </row>
@@ -1705,6 +1814,9 @@
         <v>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</v>
       </c>
       <c r="K37" t="str">
+        <v>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L37" t="str">
         <v>/images/products/prod_046_1_12-l0LZzxDB78A0b3ENPw61IPM1TbNp-e.jpg</v>
       </c>
     </row>
@@ -1740,6 +1852,9 @@
         <v>Elegant and comfortable girls cycle featuring low step-through frame, comfortable upright geometry, rear carrier, and smooth brake controls.</v>
       </c>
       <c r="K38" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L38" t="str">
         <v>/images/products/prod_047_1_12dXbchyMT1JX3me2LR2NMcyZY9LlvDvG.jpg,/images/products/prod_047_2_1ZloQm8BkEBmS1dycx5Gt0-2Pkmm4oW7k.jpg</v>
       </c>
     </row>
@@ -1775,6 +1890,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K39" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L39" t="str">
         <v>/images/products/prod_048_1_1q9hYp6kdJYhpvmBvWxFKHGGbUYovFiXh.jpg</v>
       </c>
     </row>
@@ -1810,6 +1928,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Power Brakes, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K40" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L40" t="str">
         <v>/images/products/prod_049_1_17DZ0XXndgxQv-Za--OftlEZ4Jo9MLJLK.jpg,/images/products/prod_049_2_1qV2Wmetczbft1-kyA6E2yKZ-X_QJYHWM.jpg</v>
       </c>
     </row>
@@ -1845,6 +1966,9 @@
         <v>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Front &amp; Rear Mechanical Power Brakes, and a rigid Lightweight Aircraft-Grade Alloy Frame for fast city and trail riding.</v>
       </c>
       <c r="K41" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L41" t="str">
         <v>/images/products/prod_052_1_105NvCgjVtXGtaeqUeDr858YjfsaNBmNa.jpg</v>
       </c>
     </row>
@@ -1880,6 +2004,9 @@
         <v>High-performance geared cycle built with Multi-Speed Gear System, Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</v>
       </c>
       <c r="K42" t="str">
+        <v>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Multi-Speed Gear System | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L42" t="str">
         <v>/images/products/prod_054_1.jpg</v>
       </c>
     </row>
@@ -1915,6 +2042,9 @@
         <v>AOKI Street Mamba is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K43" t="str">
+        <v>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L43" t="str">
         <v>/images/products/prod_055_1.jpg,/images/products/prod_055_2.jpg</v>
       </c>
     </row>
@@ -1950,6 +2080,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Power Brakes, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K44" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L44" t="str">
         <v>/images/products/prod_056_1_1Ws3eOH-sOZouOZB14wePKR-eqO69kGwH.jpg</v>
       </c>
     </row>
@@ -1985,6 +2118,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K45" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L45" t="str">
         <v>/images/products/prod_057_1_1k1yFIJJdHeoq9OAfD4q2lDOsT0I7j1Mf.jpg,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg</v>
       </c>
     </row>
@@ -2020,6 +2156,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K46" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L46" t="str">
         <v>/images/products/prod_058_1_19hv2ju_nqrZGcVFJCD0fotD41RiwWNuc.jpg,/images/products/prod_058_2_1OT8rO3PDeCLBzsLHMUWJ_UyCckcc6lX2.jpg</v>
       </c>
     </row>
@@ -2055,6 +2194,9 @@
         <v>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K47" t="str">
+        <v>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L47" t="str">
         <v>https://drive.google.com/file/d//view?usp=sharing,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg</v>
       </c>
     </row>
@@ -2090,6 +2232,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Power Brakes, and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K48" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L48" t="str">
         <v>/images/products/prod_062_1.jpg</v>
       </c>
     </row>
@@ -2125,6 +2270,9 @@
         <v>AOKI Street Gost is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K49" t="str">
+        <v>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L49" t="str">
         <v>/images/products/prod_064_1.jpg</v>
       </c>
     </row>
@@ -2160,6 +2308,9 @@
         <v>Hercules Hardstyle 27.5t EC Non Sus DD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K50" t="str">
+        <v>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L50" t="str">
         <v>/images/products/prod_049_1_1ixyGkpCmUa9Md78oqjMOHj42I4tFqD0S.jpg</v>
       </c>
     </row>
@@ -2195,6 +2346,9 @@
         <v>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</v>
       </c>
       <c r="K51" t="str">
+        <v>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</v>
+      </c>
+      <c r="L51" t="str">
         <v>/images/products/prod_050_1_168Y_oxmz0eUB7UldAykn2oXjREuOzDWJ.jpg,/images/products/prod_050_2_13OKzmHpJoh0_SJpkc89YiaGslaRe_ivZ.jpg</v>
       </c>
     </row>
@@ -2230,12 +2384,15 @@
         <v>Beeride Luminious 26T FSDD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</v>
       </c>
       <c r="K52" t="str">
+        <v>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</v>
+      </c>
+      <c r="L52" t="str">
         <v>/images/products/prod_051_1_1DofcHHbhKLTZgifImBQg5JxfboSO0BGC.jpg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L52"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/store_inventory_template.xlsx
+++ b/store_inventory_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="338">
   <si>
     <t>product_id</t>
   </si>
@@ -53,7 +53,128 @@
     <t>prod_001</t>
   </si>
   <si>
-    <t>91 ALPHA BOMBAY 26T VB</t>
+    <t>AVON CAMILA IBC 26T LADY</t>
+  </si>
+  <si>
+    <t>AVON</t>
+  </si>
+  <si>
+    <t>cat_004</t>
+  </si>
+  <si>
+    <t>26T</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>15+ Years</t>
+  </si>
+  <si>
+    <t>Elegant and comfortable girls cycle featuring low step-through frame, comfortable upright geometry, rear carrier, and smooth brake controls.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Front &amp; Rear Caliper Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 13+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_009_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_002</t>
+  </si>
+  <si>
+    <t>BSA HAZEL LADY BIRLD 26T</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Front &amp; Rear Caliper Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1vVh5dhYsLLm5a_Io-6G4wcSBCcomh9EF/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1P8Ey7pMJ5ZYgCf2N2LjXEOoK2LIki8ZH/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1P8Ey7pMJ5ZYgCf2N2LjXEOoK2LIki8ZH/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_003</t>
+  </si>
+  <si>
+    <t>BSA DIVA LADY BIRLD 26T</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1qRa0nX4auwLeNEowqS1HXRTny6FHqXjw/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/15smTQULrzUJ-x-lWRalf4O-7Me7tjqKS/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1thjs6ii90VsPnEXP9DYlnJw10oJFCktR/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_004</t>
+  </si>
+  <si>
+    <t>91 ALPHA BOMBAY 26T VB IBC</t>
   </si>
   <si>
     <t>ALPHA</t>
@@ -62,430 +183,657 @@
     <t>cat_002</t>
   </si>
   <si>
-    <t>26T</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>15+ Years</t>
-  </si>
-  <si>
-    <t>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+    <t>Durable and stylish adult cycle engineered with  Hi-Tensile Steel Frame, High-Performance V-Brake System, and sleek geometry for daily commutes and fitness rides.</t>
   </si>
   <si>
     <t>/images/products/prod_001_1_1cBHXAZIQpKTodzPqbos1Ngp1sV-MFDwC.jpg,/images/products/prod_001_2_1Iv7MRj7lY8BSTD19GLEGM0ZcK6zuQYd1.jpg</t>
   </si>
   <si>
-    <t>prod_002</t>
-  </si>
-  <si>
-    <t>TORONTO SKYWALK 20T</t>
-  </si>
-  <si>
-    <t>TORONTO</t>
+    <t>prod_005</t>
+  </si>
+  <si>
+    <t>HERCULES REDEEM 26T VB IBC</t>
+  </si>
+  <si>
+    <t>HERCULES</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_034_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_006</t>
+  </si>
+  <si>
+    <t>91 ALPHA CAIRO 26T FSDD 3.00 IBC</t>
+  </si>
+  <si>
+    <t>Durable and stylish adult cycle engineered with Hi-Tensile Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_006_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_007</t>
+  </si>
+  <si>
+    <t>HERCULES REDEEM 26T DD IBC</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_019_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_008</t>
+  </si>
+  <si>
+    <t>HERCULES RIFT FS DD 26T IBC</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_040_1_1g-pYq_s7n50qf5m2eJN9l5r_v4edU99Z.jpg</t>
+  </si>
+  <si>
+    <t>prod_009</t>
+  </si>
+  <si>
+    <t>STRYDER NEUTRON 26 FSDD IBC</t>
+  </si>
+  <si>
+    <t>STRYDER</t>
+  </si>
+  <si>
+    <t>cat_003</t>
+  </si>
+  <si>
+    <t>Wheel Size: Standard Size | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Multi-Speed Gear System | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_054_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_010</t>
+  </si>
+  <si>
+    <t>91 ALPHA BOMBAY 26T FSDD IBC</t>
+  </si>
+  <si>
+    <t>/images/products/prod_057_1_1k1yFIJJdHeoq9OAfD4q2lDOsT0I7j1Mf.jpg,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg</t>
+  </si>
+  <si>
+    <t>prod_011</t>
+  </si>
+  <si>
+    <t>BSA HAZEL LADY BIRLD 24T</t>
+  </si>
+  <si>
+    <t>24T</t>
+  </si>
+  <si>
+    <t>12-15 Years</t>
+  </si>
+  <si>
+    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Front &amp; Rear Caliper Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 10-13 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_047_1_12dXbchyMT1JX3me2LR2NMcyZY9LlvDvG.jpg,/images/products/prod_047_2_1ZloQm8BkEBmS1dycx5Gt0-2Pkmm4oW7k.jpg</t>
+  </si>
+  <si>
+    <t>prod_012</t>
+  </si>
+  <si>
+    <t>BSA DIVA LADY BIRLD 24T</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1qRa0nX4auwLeNEowqS1HXRTny6FHqXjw/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/15smTQULrzUJ-x-lWRalf4O-7Me7tjqKS/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1thjs6ii90VsPnEXP9DYlnJw10oJFCktR/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_013</t>
+  </si>
+  <si>
+    <t>AVON RABIA IBC 24T IBC LADY</t>
+  </si>
+  <si>
+    <t>/images/products/prod_012_1.jpg,/images/products/prod_012_2.jpg,/images/products/prod_012_3.jpg</t>
+  </si>
+  <si>
+    <t>prod_014</t>
+  </si>
+  <si>
+    <t>91 ALPHA BOMBAY 24T VB IBC</t>
+  </si>
+  <si>
+    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_058_1_19hv2ju_nqrZGcVFJCD0fotD41RiwWNuc.jpg,/images/products/prod_058_2_1OT8rO3PDeCLBzsLHMUWJ_UyCckcc6lX2.jpg</t>
+  </si>
+  <si>
+    <t>prod_015</t>
+  </si>
+  <si>
+    <t>HERCULES RIFT VB 24T IBC</t>
+  </si>
+  <si>
+    <t>/images/products/prod_032_1_1rYYvmQpehc6qpBH7YOz0jT_aI1uTEsOQ.jpg,/images/products/prod_032_2_1qSfD9okHkQmY7E8OFcqcUlRURRiPHH8D.jpg</t>
+  </si>
+  <si>
+    <t>prod_016</t>
+  </si>
+  <si>
+    <t>91 ALPHA CAIRO 24T FSDD 3.00 IBC</t>
+  </si>
+  <si>
+    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_005_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_017</t>
+  </si>
+  <si>
+    <t>HERCULES RIFT FS DD 24T IBC</t>
+  </si>
+  <si>
+    <t>/images/products/prod_030_1_1qVziSjWYCGFf8R3oIKmAzKjvcNZu0KnG.jpg</t>
+  </si>
+  <si>
+    <t>prod_018</t>
+  </si>
+  <si>
+    <t>HERCULES Redeem 24T FX DD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1DSAO0nYsjo_lUun8oHcnDVgHuseZigZF/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1Uc9i16VJL7x6MRicubCox3rzPCgfci6l/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1NP43At8iw8DhG8mD36hden5Yx17ruTVx/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_019</t>
+  </si>
+  <si>
+    <t>KEYSTO CYLER SS 24T FSDD</t>
+  </si>
+  <si>
+    <t>KEYSTO</t>
+  </si>
+  <si>
+    <t>/images/products/prod_020_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_020</t>
+  </si>
+  <si>
+    <t>91 ALPHA BOMBAY 24T FSDD IBC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1rqlXDSHosZ5XriBsB4H5YwCxulGqYHJI/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1he5A6gyOzf-7dJ79Y8cPnLCbQ5uOVxB1/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1BDaoJLTecsUa9cpY6lVMYINAbjhO-Pdi/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1uLMRmWn138gKZostfy4Dv5PK0RpgvDZI/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_021</t>
+  </si>
+  <si>
+    <t>BSA CHAMP 12T</t>
   </si>
   <si>
     <t>cat_001</t>
   </si>
   <si>
+    <t>12T</t>
+  </si>
+  <si>
+    <t>2-5 Years</t>
+  </si>
+  <si>
+    <t>Sturdy and safe kids cycle designed for young riders (2-5 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 12 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_014_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_022</t>
+  </si>
+  <si>
+    <t>OYEKID Shark Tank 14T IBC</t>
+  </si>
+  <si>
+    <t>OYEKID</t>
+  </si>
+  <si>
+    <t>14T</t>
+  </si>
+  <si>
+    <t>Wheel Size: 14 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1AdOfZ4Zbsou5MwFk360oq74SPZWn_FZw/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/15znf4GTBjl_YImUkW81R4VjjeNCLE4vj/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1tx3X6hyUBts5bsLjPOa030vvxMMFiQLl/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_023</t>
+  </si>
+  <si>
+    <t>OYEKID Swag 14T IBC</t>
+  </si>
+  <si>
+    <t>Wheel Size: 14 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1yXVopctXMmWp-DcPa1O9VkkXOZRtKqJk/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1oHGXPX1S-8a5Snow1w_vh1i1rZDZt4eB/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/10qLtBNcOAvve1Oqe52lRfuPC3n78gxk_/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_024</t>
+  </si>
+  <si>
+    <t>BSA CHAMP 14T</t>
+  </si>
+  <si>
+    <t>/images/products/prod_015_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_025</t>
+  </si>
+  <si>
+    <t>PILLER TUSCAN 14T DLX</t>
+  </si>
+  <si>
+    <t>PILLER</t>
+  </si>
+  <si>
+    <t>/images/products/prod_035_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_026</t>
+  </si>
+  <si>
+    <t>OYEKID Shark Tank 16T IBC</t>
+  </si>
+  <si>
+    <t>16T</t>
+  </si>
+  <si>
+    <t>5-8 Years</t>
+  </si>
+  <si>
+    <t>Sturdy and safe kids cycle designed for young riders (5-8 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 16 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 5-8 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1FAJsIYmp0i85iLwUrKeTNvhwkR1wWX6t/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1FAJsIYmp0i85iLwUrKeTNvhwkR1wWX6t/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1gVNgr5E2UVNC4azPA3_4CAX5QkpIZ-4k/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_027</t>
+  </si>
+  <si>
+    <t>STRYDER 16T Arche IC Kids</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1ZPDxkx730W7rjPJEfOnIw7upiBGUa3Qr/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1Mz6wlkb1shJNDTHy9F-bpOYon6vRDHD0/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1cC5VhrzyKblOYKX-soJxShAoKmoKkyUN/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_028</t>
+  </si>
+  <si>
+    <t>BSA CHAMP 16T</t>
+  </si>
+  <si>
+    <t>/images/products/prod_016_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_029</t>
+  </si>
+  <si>
+    <t>PILLER TUSCAN 16T DLX</t>
+  </si>
+  <si>
+    <t>/images/products/prod_037_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_030</t>
+  </si>
+  <si>
+    <t>KEYSTO FRIENDS 20T</t>
+  </si>
+  <si>
     <t>20T</t>
   </si>
   <si>
-    <t>TRUE</t>
-  </si>
-  <si>
     <t>8-12 Years</t>
   </si>
   <si>
     <t>Sturdy and safe kids cycle designed for young riders (8-12 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</t>
   </si>
   <si>
-    <t>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_002_1_1UMFTn5JP9w2FFi4KL6l-8diVc5gUkx-Z.jpg</t>
-  </si>
-  <si>
-    <t>prod_003</t>
-  </si>
-  <si>
-    <t>91 ALPHA CAIRO 24T FSDD 3.00</t>
-  </si>
-  <si>
-    <t>24T</t>
-  </si>
-  <si>
-    <t>12-15 Years</t>
-  </si>
-  <si>
-    <t>Durable and stylish adult cycle engineered with High-Tensile Carbon Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_005_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_004</t>
-  </si>
-  <si>
-    <t>91 ALPHA CAIRO 26T FSDD 3.00</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_006_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_005</t>
-  </si>
-  <si>
-    <t>AVON CAMILA IBC 26T</t>
-  </si>
-  <si>
-    <t>AVON</t>
-  </si>
-  <si>
-    <t>cat_004</t>
-  </si>
-  <si>
-    <t>Elegant and comfortable girls cycle featuring low step-through frame, comfortable upright geometry, rear carrier, and smooth brake controls.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_009_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_006</t>
-  </si>
-  <si>
-    <t>AVON INSPIRO 20T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_011_1.jpg,/images/products/prod_011_2.jpg,/images/products/prod_011_3_1mab42s_Mf84sxHNRZbtB6q6yn-2m0tMB.jpg</t>
-  </si>
-  <si>
-    <t>prod_007</t>
-  </si>
-  <si>
-    <t>AVON RABIA IBC 24T</t>
-  </si>
-  <si>
-    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_012_1.jpg,/images/products/prod_012_2.jpg,/images/products/prod_012_3.jpg</t>
-  </si>
-  <si>
-    <t>prod_008</t>
-  </si>
-  <si>
-    <t>AVON YAMA 26T FAT</t>
-  </si>
-  <si>
-    <t>cat_003</t>
-  </si>
-  <si>
-    <t>Avon Yama 26T FAT is a rugged fat-tire bicycle featuring extra-wide 4.0" all-terrain tires, heavy-duty suspension, and 21-speed gears for ultimate traction and off-road dominance.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Multi-Speed Gear System | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</t>
-  </si>
-  <si>
-    <t>/images/products/prod_013_1.jpg,/images/products/prod_013_2.jpg,/images/products/prod_013_3.jpg</t>
-  </si>
-  <si>
-    <t>prod_009</t>
-  </si>
-  <si>
-    <t>BSA CHAMP 12T</t>
-  </si>
-  <si>
-    <t>BSA</t>
-  </si>
-  <si>
-    <t>12T</t>
-  </si>
-  <si>
-    <t>2-5 Years</t>
-  </si>
-  <si>
-    <t>Sturdy and safe kids cycle designed for young riders (2-5 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 12 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_014_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_010</t>
-  </si>
-  <si>
-    <t>BSA CHAMP 14T</t>
-  </si>
-  <si>
-    <t>14T</t>
-  </si>
-  <si>
-    <t>Wheel Size: 14 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 2-5 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_015_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_011</t>
-  </si>
-  <si>
-    <t>BSA CHAMP 16T</t>
-  </si>
-  <si>
-    <t>16T</t>
-  </si>
-  <si>
-    <t>5-8 Years</t>
-  </si>
-  <si>
-    <t>Sturdy and safe kids cycle designed for young riders (5-8 Years). Equipped with anti-skid tires, full chain guard, and ergonomic safety grips.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 16 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 5-8 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_016_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_012</t>
-  </si>
-  <si>
-    <t>BSA KINDER 20T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_017_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_013</t>
-  </si>
-  <si>
-    <t>BSA ROCKET IC 20T CB IBC</t>
-  </si>
-  <si>
-    <t>Wheel Size: 20 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Caliper Brakes with Soft-Grip Rubber Pads | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_018_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_014</t>
-  </si>
-  <si>
-    <t>HERCULES REDEEM 26T DD IBC</t>
-  </si>
-  <si>
-    <t>HERCULES</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_019_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_015</t>
-  </si>
-  <si>
-    <t>KEYSTO CYLER SS 24T FSDD</t>
-  </si>
-  <si>
-    <t>KEYSTO</t>
-  </si>
-  <si>
-    <t>/images/products/prod_020_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_016</t>
-  </si>
-  <si>
-    <t>MONTRA HYPNO PRO 27T EC</t>
-  </si>
-  <si>
-    <t>MONTRA</t>
-  </si>
-  <si>
-    <t>cat_005</t>
-  </si>
-  <si>
-    <t>27.5T</t>
-  </si>
-  <si>
-    <t>Montra Hypno PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 27.5 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_021_1.jpg,/images/products/prod_021_2.jpg</t>
-  </si>
-  <si>
-    <t>prod_017</t>
-  </si>
-  <si>
-    <t>BSA VIONA 26T</t>
-  </si>
-  <si>
-    <t>BSA Viona 26T is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_022_1.jpg,/images/products/prod_022_2.jpg,/images/products/prod_022_3.jpg</t>
-  </si>
-  <si>
-    <t>prod_018</t>
-  </si>
-  <si>
-    <t>RALEIGH NAVARRO ONE 29T (D/Disc)</t>
-  </si>
-  <si>
-    <t>RALEIGH</t>
-  </si>
-  <si>
-    <t>29T</t>
-  </si>
-  <si>
-    <t>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_024_1.jpg,/images/products/prod_024_2.jpg,/images/products/prod_024_3.jpg</t>
-  </si>
-  <si>
-    <t>prod_019</t>
-  </si>
-  <si>
-    <t>MAEVE 26T EC</t>
-  </si>
-  <si>
-    <t>Maeve 26T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>/images/products/prod_025_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_020</t>
-  </si>
-  <si>
-    <t>TORONTO FRASER FSDD 29" 21 Speed</t>
-  </si>
-  <si>
-    <t>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_027_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_021</t>
-  </si>
-  <si>
-    <t>HERCULES BRUTE 27T FSDD  EC</t>
-  </si>
-  <si>
-    <t>Hercules Brute 27T FSDD EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_029_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_022</t>
-  </si>
-  <si>
-    <t>POPSTAR FLORENCE 20T</t>
-  </si>
-  <si>
-    <t>POPSTAR</t>
-  </si>
-  <si>
-    <t>/images/products/prod_030_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_023</t>
-  </si>
-  <si>
-    <t>NINETY ONE  CHAMP 20T</t>
-  </si>
-  <si>
-    <t>NINETY ONE</t>
-  </si>
-  <si>
-    <t>/images/products/prod_031_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_024</t>
-  </si>
-  <si>
-    <t>HERCULES HARDSTYLE PRO 27T EC</t>
-  </si>
-  <si>
-    <t>Hercules Hardstyle PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_032_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_025</t>
-  </si>
-  <si>
-    <t>HERCULES REDEEM 27T DD 21S</t>
-  </si>
-  <si>
-    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_033_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_026</t>
-  </si>
-  <si>
-    <t>HERCULES REDEEM 26T VB IBC</t>
-  </si>
-  <si>
-    <t>/images/products/prod_034_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_027</t>
-  </si>
-  <si>
-    <t>PILLER TUSCAN 14T DLX</t>
-  </si>
-  <si>
-    <t>PILLER</t>
-  </si>
-  <si>
-    <t>/images/products/prod_035_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_028</t>
+    <t>Wheel Size: 20 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Calibrated Caliper Brakes with Child-Safe Levers | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 8-12 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_046_1_12-l0LZzxDB78A0b3ENPw61IPM1TbNp-e.jpg</t>
+  </si>
+  <si>
+    <t>prod_031</t>
+  </si>
+  <si>
+    <t>BSA Warbot 20T</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1zH23DBq2CSeZsti90fpAC5FMPbebUazC/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1FEXtc6RsTzTTs5uC9DhBiK6pYnyBtiVk/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_032</t>
+  </si>
+  <si>
+    <t>OYEKID Swag 20T IBC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1N_4EPwxyl9CRg1MIM2ZliIZCrrERzVYt/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1HIJ9Ras4TZUma587gWZUTdoIJHPzB4CO/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1W5Ycrs68zeof1slJKdm60_jN6nKn7ZFY/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1gBqzWs03KJYlwTvDj2ae1pLOoiB-lv9M/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_033</t>
   </si>
   <si>
     <t>PILLER TUSCAN 20T DLX</t>
@@ -494,298 +842,19 @@
     <t>/images/products/prod_036_1.jpg</t>
   </si>
   <si>
-    <t>prod_029</t>
-  </si>
-  <si>
-    <t>PILLER TUSCAN 16T DLX</t>
-  </si>
-  <si>
-    <t>/images/products/prod_037_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_030</t>
-  </si>
-  <si>
-    <t>HERCULES RIFT FS DD 24T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_030_1_1qVziSjWYCGFf8R3oIKmAzKjvcNZu0KnG.jpg</t>
-  </si>
-  <si>
-    <t>prod_031</t>
-  </si>
-  <si>
-    <t>HERCULES RIFT FS DD 26T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_040_1_1g-pYq_s7n50qf5m2eJN9l5r_v4edU99Z.jpg</t>
-  </si>
-  <si>
-    <t>prod_032</t>
-  </si>
-  <si>
-    <t>HERCULES RIFT VB 24T</t>
-  </si>
-  <si>
-    <t>Wheel Size: 24 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: High-Performance V-Brake System | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 12-15 Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_032_1_1rYYvmQpehc6qpBH7YOz0jT_aI1uTEsOQ.jpg,/images/products/prod_032_2_1qSfD9okHkQmY7E8OFcqcUlRURRiPHH8D.jpg</t>
-  </si>
-  <si>
-    <t>prod_033</t>
-  </si>
-  <si>
-    <t>HERCULES REDEEM 26T FSDD 21 GEAR</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_042_1_1VGfMRvQitXL1aQYdeM933R_pw4jiJXss.jpg</t>
-  </si>
-  <si>
     <t>prod_034</t>
   </si>
   <si>
-    <t>Hercules Shurveer EC</t>
-  </si>
-  <si>
-    <t>Hercules Shurveer EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_043_1_18abkEN_bcgrKPFHkF5ttxu6aWRIccoNj.jpg</t>
+    <t>BSA Bestie 20T</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SwIHXNAx1-1RNrMZeQj-h975_irnf2oj/view?usp=sharing</t>
   </si>
   <si>
     <t>prod_035</t>
   </si>
   <si>
-    <t>RALEIGH E-SURGE S/S ECO</t>
-  </si>
-  <si>
-    <t>Raleigh E-surge S/s Eco is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: Standard Size | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_044_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_036</t>
-  </si>
-  <si>
-    <t>KEYSTO FRIENDS 20T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_046_1_12-l0LZzxDB78A0b3ENPw61IPM1TbNp-e.jpg</t>
-  </si>
-  <si>
-    <t>prod_037</t>
-  </si>
-  <si>
-    <t>BSA HAZEL LADY BIRLD 24T</t>
-  </si>
-  <si>
-    <t>/images/products/prod_047_1_12dXbchyMT1JX3me2LR2NMcyZY9LlvDvG.jpg,/images/products/prod_047_2_1ZloQm8BkEBmS1dycx5Gt0-2Pkmm4oW7k.jpg</t>
-  </si>
-  <si>
-    <t>prod_038</t>
-  </si>
-  <si>
-    <t>SUNCROSS HURRICANE FSDD 26T</t>
-  </si>
-  <si>
-    <t>SUNCROSS</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_048_1_1q9hYp6kdJYhpvmBvWxFKHGGbUYovFiXh.jpg</t>
-  </si>
-  <si>
-    <t>prod_039</t>
-  </si>
-  <si>
-    <t>RALEIGH EXALT 29T SS</t>
-  </si>
-  <si>
-    <t>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Power Brakes, and sleek geometry for daily commutes and fitness rides.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_049_1_17DZ0XXndgxQv-Za--OftlEZ4Jo9MLJLK.jpg,/images/products/prod_049_2_1qV2Wmetczbft1-kyA6E2yKZ-X_QJYHWM.jpg</t>
-  </si>
-  <si>
-    <t>prod_040</t>
-  </si>
-  <si>
-    <t>RALEIGH NAVARRO ONE 29T M/S</t>
-  </si>
-  <si>
-    <t>High-performance geared cycle built with 21-Speed Gear System (Shimano / Microshift), Front &amp; Rear Mechanical Power Brakes, and a rigid Lightweight Aircraft-Grade Alloy Frame for fast city and trail riding.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: 21-Speed Gear System (Shimano / Microshift) | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_052_1_105NvCgjVtXGtaeqUeDr858YjfsaNBmNa.jpg</t>
-  </si>
-  <si>
-    <t>prod_041</t>
-  </si>
-  <si>
-    <t>STRYDER NEUTRON 26 FSDD SS</t>
-  </si>
-  <si>
-    <t>STRYDER</t>
-  </si>
-  <si>
-    <t>High-performance geared cycle built with Multi-Speed Gear System, Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Carbon Steel Frame for fast city and trail riding.</t>
-  </si>
-  <si>
-    <t>Wheel Size: Standard Size | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Multi-Speed Gear System | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_054_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_042</t>
-  </si>
-  <si>
-    <t>AOKI STREET MAMBA</t>
-  </si>
-  <si>
-    <t>AOKI</t>
-  </si>
-  <si>
-    <t>AOKI Street Mamba is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>/images/products/prod_055_1.jpg,/images/products/prod_055_2.jpg</t>
-  </si>
-  <si>
-    <t>prod_043</t>
-  </si>
-  <si>
-    <t>RALEIGH NAVARRO ONE 29T SS</t>
-  </si>
-  <si>
-    <t>/images/products/prod_056_1_1Ws3eOH-sOZouOZB14wePKR-eqO69kGwH.jpg</t>
-  </si>
-  <si>
-    <t>prod_044</t>
-  </si>
-  <si>
-    <t>91 ALPHA BOMBAY 26T FSDD</t>
-  </si>
-  <si>
-    <t>/images/products/prod_057_1_1k1yFIJJdHeoq9OAfD4q2lDOsT0I7j1Mf.jpg,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg</t>
-  </si>
-  <si>
-    <t>prod_045</t>
-  </si>
-  <si>
-    <t>91 ALPHA BOMBAY 24T VB</t>
-  </si>
-  <si>
-    <t>/images/products/prod_058_1_19hv2ju_nqrZGcVFJCD0fotD41RiwWNuc.jpg,/images/products/prod_058_2_1OT8rO3PDeCLBzsLHMUWJ_UyCckcc6lX2.jpg</t>
-  </si>
-  <si>
-    <t>prod_046</t>
-  </si>
-  <si>
-    <t>91 ALPHA BOMBAY 24T FSDD</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d//view?usp=sharing,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg,/images/products/prod_057_2_1iPIByYnUQzn3NtdOw85C-0Tfd93VRUsN.jpg</t>
-  </si>
-  <si>
-    <t>prod_047</t>
-  </si>
-  <si>
-    <t>RALEIGH PHASE PRO 29TS/S</t>
-  </si>
-  <si>
-    <t>/images/products/prod_062_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_048</t>
-  </si>
-  <si>
-    <t>AOKI STREET GOST</t>
-  </si>
-  <si>
-    <t>AOKI Street Gost is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>/images/products/prod_064_1.jpg</t>
-  </si>
-  <si>
-    <t>prod_049</t>
-  </si>
-  <si>
-    <t>HERCULES HARDSTYLE 27.5T EC Non SUS DD</t>
-  </si>
-  <si>
-    <t>Hercules Hardstyle 27.5t EC Non Sus DD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_049_1_1ixyGkpCmUa9Md78oqjMOHj42I4tFqD0S.jpg</t>
-  </si>
-  <si>
-    <t>prod_050</t>
-  </si>
-  <si>
-    <t>RALEIGH CAPTUS 29T FSDD SS</t>
-  </si>
-  <si>
-    <t>Wheel Size: 29 Inches | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_050_1_168Y_oxmz0eUB7UldAykn2oXjREuOzDWJ.jpg,/images/products/prod_050_2_13OKzmHpJoh0_SJpkc89YiaGslaRe_ivZ.jpg</t>
-  </si>
-  <si>
-    <t>prod_051</t>
-  </si>
-  <si>
-    <t>BEERIDE Luminious 26T FSDD</t>
-  </si>
-  <si>
-    <t>BEERIDE</t>
-  </si>
-  <si>
-    <t>Beeride Luminious 26T FSDD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
-  </si>
-  <si>
-    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
-  </si>
-  <si>
-    <t>/images/products/prod_051_1_1DofcHHbhKLTZgifImBQg5JxfboSO0BGC.jpg</t>
-  </si>
-  <si>
-    <t>prod_052</t>
-  </si>
-  <si>
-    <t>BSA Bestie</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1SwIHXNAx1-1RNrMZeQj-h975_irnf2oj/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>prod_053</t>
-  </si>
-  <si>
-    <t>BSA Spinto</t>
+    <t>BSA Spinto 20T</t>
   </si>
   <si>
     <r>
@@ -810,31 +879,546 @@
     </r>
   </si>
   <si>
+    <t>prod_036</t>
+  </si>
+  <si>
+    <t>BSA Hacker 20T</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mC9U0XWMr_EBsfgdphovjsPYMteb3eaT/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>prod_037</t>
+  </si>
+  <si>
+    <t>BSA Ambush 20T</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aBHgvroGst-BrSpkD4g7N_vNKrG7624V/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>prod_038</t>
+  </si>
+  <si>
+    <t>BSA Roamer 20T</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WRYU49dYg-337MK5lB1KgfTu2PFCtgOR/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>prod_039</t>
+  </si>
+  <si>
+    <t>TORONTO SKYWALK 20T</t>
+  </si>
+  <si>
+    <t>TORONTO</t>
+  </si>
+  <si>
+    <t>/images/products/prod_002_1_1UMFTn5JP9w2FFi4KL6l-8diVc5gUkx-Z.jpg</t>
+  </si>
+  <si>
+    <t>prod_040</t>
+  </si>
+  <si>
+    <t>prod_041</t>
+  </si>
+  <si>
+    <t>AVON INSPIRO 20T DX IBC</t>
+  </si>
+  <si>
+    <t>/images/products/prod_011_1.jpg,/images/products/prod_011_2.jpg,/images/products/prod_011_3_1mab42s_Mf84sxHNRZbtB6q6yn-2m0tMB.jpg</t>
+  </si>
+  <si>
+    <t>prod_042</t>
+  </si>
+  <si>
+    <t>BSA KINDER 20T</t>
+  </si>
+  <si>
+    <t>/images/products/prod_017_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_043</t>
+  </si>
+  <si>
+    <t>BSA ROCKET IC 20T CB IBC</t>
+  </si>
+  <si>
+    <t>/images/products/prod_018_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_044</t>
+  </si>
+  <si>
+    <t>POPSTAR FLORENCE 20T</t>
+  </si>
+  <si>
+    <t>POPSTAR</t>
+  </si>
+  <si>
+    <t>/images/products/prod_030_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_045</t>
+  </si>
+  <si>
+    <t>NINETY ONE  CHAMP 20T</t>
+  </si>
+  <si>
+    <t>/images/products/prod_031_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_046</t>
+  </si>
+  <si>
+    <t>AOKI STREET GOST</t>
+  </si>
+  <si>
+    <t>AOKI</t>
+  </si>
+  <si>
+    <t>cat_005</t>
+  </si>
+  <si>
+    <t>AOKI Street Gost is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 20 Inches | Frame Material: High-Tensile Alloy Frame | Brake System: Front &amp; Rear Mechanical  Hydraulic Disc Brakes| Gears / Speed: 7Speed Direct Drive | Front Suspension: Front &amp; Hydraulic Dual Rear Suspension | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 48V 250W High Torque BLDC Hub Drive Motor | Battery Unit: Removable 48V 15.6AH Highly Efficient Li Ion Portable Battery | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h | Rang :105 KM on Pedal Assist Mode and 80 KM on Throttle</t>
+  </si>
+  <si>
+    <t>/images/products/prod_064_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_047</t>
+  </si>
+  <si>
+    <t>BEERIDE Luminious 26T FSDD EC</t>
+  </si>
+  <si>
+    <t>BEERIDE</t>
+  </si>
+  <si>
+    <t>Beeride Luminious 26T FSDD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V 7.8 AH Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h | Rang 35 km</t>
+  </si>
+  <si>
+    <t>/images/products/prod_051_1_1DofcHHbhKLTZgifImBQg5JxfboSO0BGC.jpg</t>
+  </si>
+  <si>
+    <t>prod_048</t>
+  </si>
+  <si>
+    <t>AOKI STREET MAMBA EC</t>
+  </si>
+  <si>
+    <t>AOKI Street Mamba is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>/images/products/prod_055_1.jpg,/images/products/prod_055_2.jpg</t>
+  </si>
+  <si>
+    <t>prod_049</t>
+  </si>
+  <si>
+    <t>RALEIGH E-SURGE S/S ECO EC</t>
+  </si>
+  <si>
+    <t>RALEIGH</t>
+  </si>
+  <si>
+    <t>27.5T</t>
+  </si>
+  <si>
+    <t>Raleigh E-surge S/s Eco is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: Standard Size | Frame Material: Lightweight Aircraft-Grade Alloy Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_044_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_050</t>
+  </si>
+  <si>
+    <t>MONTRA HYPNO PRO 27T EC</t>
+  </si>
+  <si>
+    <t>MONTRA</t>
+  </si>
+  <si>
+    <t>Montra Hypno PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 27.5 Inches | Frame Material: Lightweight Aircraft-Grade Steel Frame | Brake System: Front &amp; Rear Mechanical Disc Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Threadless Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: 12Ah LFP Removable Battery | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_021_1.jpg,/images/products/prod_021_2.jpg</t>
+  </si>
+  <si>
+    <t>prod_051</t>
+  </si>
+  <si>
+    <t>Hercules Shurveer EC</t>
+  </si>
+  <si>
+    <t>Hercules Shurveer EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: Standard Size | Frame Material: High-Tensile Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V 6Ah Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_043_1_18abkEN_bcgrKPFHkF5ttxu6aWRIccoNj.jpg</t>
+  </si>
+  <si>
+    <t>prod_052</t>
+  </si>
+  <si>
+    <t>HERCULES HARDSTYLE PRO 27T EC</t>
+  </si>
+  <si>
+    <t>Hercules Hardstyle PRO 27T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_032_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_053</t>
+  </si>
+  <si>
+    <t>HERCULES BRUTE 27T FSDD  EC</t>
+  </si>
+  <si>
+    <t>Hercules Brute 27T FSDD EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_029_1.jpg</t>
+  </si>
+  <si>
     <t>prod_054</t>
   </si>
   <si>
-    <t>BSA Hacker</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1mC9U0XWMr_EBsfgdphovjsPYMteb3eaT/view?usp=sharing</t>
+    <t>STRYDER 26T Elevate EC</t>
+  </si>
+  <si>
+    <t>Introducing the Stryder Elevate IC 26 — a premium electric cycle built for adults who demand performance, comfort, and smart technology in one powerful package. Whether you're commuting to work, exploring city streets, or cruising on weekends, the Elevate IC is engineered to elevate every ride.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: Lightweight Aircraft-Grade Steel Frame | Brake System: Front &amp; Rear Mechanical Disc Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Threadless Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: 8.7 Ah LFP Removable Battery | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF0000FF"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1aJHV7opqQzDmtaC3zqGNFzLNljiVeRV6/view?usp=sharing,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1o7MmWPG3VRFHGHG97nyNAJ5HdLJbb823/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1JRcf6q3wZP1OfT-bdEtCmC-cKUZf9kxs/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1c6JKX0kkV7T96gpWHYstcecZCqAa3aqk/view?usp=sharing</t>
+    </r>
   </si>
   <si>
     <t>prod_055</t>
   </si>
   <si>
-    <t>BSA Ambush</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1aBHgvroGst-BrSpkD4g7N_vNKrG7624V/view?usp=sharing</t>
+    <t>BSA VIONA 26T EC</t>
+  </si>
+  <si>
+    <t>BSA Viona 26T is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_022_1.jpg,/images/products/prod_022_2.jpg,/images/products/prod_022_3.jpg</t>
   </si>
   <si>
     <t>prod_056</t>
   </si>
   <si>
-    <t>BSA Roamer</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1WRYU49dYg-337MK5lB1KgfTu2PFCtgOR/view?usp=sharing</t>
+    <t>MAEVE 26T EC</t>
+  </si>
+  <si>
+    <t>Maeve 26T EC is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_025_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_057</t>
+  </si>
+  <si>
+    <t>HERCULES HARDSTYLE 27.5T EC Non SUS DD</t>
+  </si>
+  <si>
+    <t>Hercules Hardstyle 27.5t EC Non Sus DD is an advanced electric bicycle powered by a high-torque BLDC hub motor and removable lithium battery, designed for long-range commutes across Tirunelveli.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile Carbon Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Rigid Aerodynamic Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Motor Type: 36V 250W High-Torque Rear Hub BLDC Motor | Battery Unit: Removable 36V Lithium-Ion LFP Battery Pack | Riding Modes: Pedal Assist (PAS) &amp; Pure Throttle Mode | Top Speed: Up to 25 km/h</t>
+  </si>
+  <si>
+    <t>/images/products/prod_049_1_1ixyGkpCmUa9Md78oqjMOHj42I4tFqD0S.jpg</t>
+  </si>
+  <si>
+    <t>prod_058</t>
+  </si>
+  <si>
+    <t>RALEIGH NAVARRO ONE 29T M/S</t>
+  </si>
+  <si>
+    <t>29T</t>
+  </si>
+  <si>
+    <t>High-performance geared cycle built with 21-Speed Gear System (Shimano), Front &amp; Rear Mechanical Disc Brakes, and a rigid Lightweight Aircraft-Grade Alloy Frame for fast city and trail riding.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Multi-Speed Gear System | Front Suspension: Suspension Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</t>
+  </si>
+  <si>
+    <t>/images/products/prod_052_1_105NvCgjVtXGtaeqUeDr858YjfsaNBmNa.jpg</t>
+  </si>
+  <si>
+    <t>prod_059</t>
+  </si>
+  <si>
+    <t>AVON YAMA 26T FAT 21 Gear</t>
+  </si>
+  <si>
+    <t>Avon Yama 26T FAT is a rugged fat-tire bicycle featuring extra-wide 4.0" all-terrain tires, heavy-duty suspension, and 21-speed gears for ultimate traction and off-road dominance.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Disc Brakes | Gears / Speed: 21-Speed Gear System | Front Suspension: Suspension Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</t>
+  </si>
+  <si>
+    <t>/images/products/prod_013_1.jpg,/images/products/prod_013_2.jpg,/images/products/prod_013_3.jpg</t>
+  </si>
+  <si>
+    <t>prod_060</t>
+  </si>
+  <si>
+    <t>CULTSPORT Monstro 26T Fat Bike 21 Gear</t>
+  </si>
+  <si>
+    <t>CULTSPORT</t>
+  </si>
+  <si>
+    <t>CULT Monstro Fat Bike – 21 Speed Shimano Gear26T FAT is a rugged fat-tire bicycle featuring extra-wide 4.0" all-terrain tires, heavy-duty suspension, and 21-speed gears for ultimate traction and off-road dominance.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF0000FF"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1X-CrZlm8TqeS9K_GHZBHn3XZJGW7zXyO/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1F1F1F"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1DgOOTTpdYMQtoI2uR7VDGkCRKyih9_Ih/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1F1F1F"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1hMlgTfNVLsSnmKf2P3UGO4H_ufJRTEPv/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_061</t>
+  </si>
+  <si>
+    <t>SUNCROSS HURRICANE FSDD 26T IBC FAT</t>
+  </si>
+  <si>
+    <t>SUNCROSS</t>
+  </si>
+  <si>
+    <t>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Steel Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Disc Brakes | Gears / Speed: Single-Speed Gear System | Front Suspension: Suspension Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</t>
+  </si>
+  <si>
+    <t>/images/products/prod_048_1_1q9hYp6kdJYhpvmBvWxFKHGGbUYovFiXh.jpg</t>
+  </si>
+  <si>
+    <t>prod_062</t>
+  </si>
+  <si>
+    <t>TORONTO FRASER FSDD 29" 21 Speed</t>
+  </si>
+  <si>
+    <t>High-performance geared cycle built with 21-Speed Gear System (Shimano), Dual Mechanical Disc Brakes (Front &amp; Rear), and a rigid High-Tensile Steel Frame for fast city and trail riding.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_027_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_063</t>
+  </si>
+  <si>
+    <t>HERCULES REDEEM 26T FSDD 21 Gear</t>
+  </si>
+  <si>
+    <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano ) | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_042_1_1VGfMRvQitXL1aQYdeM933R_pw4jiJXss.jpg</t>
+  </si>
+  <si>
+    <t>prod_064</t>
+  </si>
+  <si>
+    <t>HERCULES REDEEM 27T DD 21S</t>
+  </si>
+  <si>
+    <t>Wheel Size: 27.5 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21-Speed Gear System (Shimano ) | Front Suspension: Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_033_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_065</t>
+  </si>
+  <si>
+    <t>RALEIGH NAVARRO ONE 29T SS</t>
+  </si>
+  <si>
+    <t>Durable and stylish adult cycle engineered with Hi-Ten Steel with Internal Cable Routing Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile  Steel Frame Frame | Brake System: Dual Mechanical Disc Brakes| Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension  Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_056_1_1Ws3eOH-sOZouOZB14wePKR-eqO69kGwH.jpg</t>
+  </si>
+  <si>
+    <t>prod_066</t>
+  </si>
+  <si>
+    <t>RALEIGH PHASE PRO 29T S/S</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_062_1.jpg</t>
+  </si>
+  <si>
+    <t>prod_067</t>
+  </si>
+  <si>
+    <t>RALEIGH EXALT 29T SS</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile  Steel Frame | Brake System:Dual Mechanical Disc Brakes | Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_049_1_17DZ0XXndgxQv-Za--OftlEZ4Jo9MLJLK.jpg,/images/products/prod_049_2_1qV2Wmetczbft1-kyA6E2yKZ-X_QJYHWM.jpg</t>
+  </si>
+  <si>
+    <t>prod_068</t>
+  </si>
+  <si>
+    <t>RALEIGH NAVARRO ONE 29T (D/Disc)</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material:High-Tensile  Steel Frame | | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_024_1.jpg,/images/products/prod_024_2.jpg,/images/products/prod_024_3.jpg</t>
+  </si>
+  <si>
+    <t>prod_069</t>
+  </si>
+  <si>
+    <t>RALEIGH CAPTUS 29T FSDD SS</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>/images/products/prod_050_1_168Y_oxmz0eUB7UldAykn2oXjREuOzDWJ.jpg,/images/products/prod_050_2_13OKzmHpJoh0_SJpkc89YiaGslaRe_ivZ.jpg</t>
+  </si>
+  <si>
+    <t>prod_070</t>
+  </si>
+  <si>
+    <t>LUCIFIRE P Pro 12 29T</t>
+  </si>
+  <si>
+    <t>LUCIFIRE</t>
+  </si>
+  <si>
+    <t>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Disc Brakes, and sleek geometry for daily commutes and fitness rides.</t>
   </si>
   <si>
     <t>slug</t>
@@ -901,7 +1485,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -914,6 +1498,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <color rgb="FF070707"/>
       <name val="Arial"/>
     </font>
@@ -922,8 +1510,15 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <u/>
+      <sz val="12.0"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -946,22 +1541,37 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1190,7 +1800,7 @@
     <col customWidth="1" min="8" max="8" width="12.78"/>
     <col customWidth="1" min="9" max="9" width="16.78"/>
     <col customWidth="1" min="10" max="10" width="149.33"/>
-    <col customWidth="1" min="11" max="11" width="383.33"/>
+    <col customWidth="1" min="11" max="11" width="227.33"/>
     <col customWidth="1" min="12" max="12" width="50.78"/>
   </cols>
   <sheetData>
@@ -1236,7 +1846,7 @@
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1249,10 +1859,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="1">
-        <v>7500.0</v>
+        <v>7800.0</v>
       </c>
       <c r="G2" s="1">
-        <v>6700.0</v>
+        <v>7350.0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>17</v>
@@ -1263,7 +1873,7 @@
       <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -1271,102 +1881,102 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2">
+        <v>9000.0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8300.0</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1">
-        <v>11200.0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>10800.0</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8400.0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7500.0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F4" s="1">
-        <v>10200.0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>9500.0</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1">
-        <v>10400.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G5" s="1">
-        <v>9700.0</v>
+        <v>6700.0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>17</v>
@@ -1374,37 +1984,37 @@
       <c r="I5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1">
-        <v>7800.0</v>
+        <v>6800.0</v>
       </c>
       <c r="G6" s="1">
-        <v>7350.0</v>
+        <v>6400.0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>17</v>
@@ -1412,595 +2022,595 @@
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>48</v>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>51</v>
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10400.0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9700.0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1">
-        <v>7900.0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6400.0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="L7" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1">
-        <v>7800.0</v>
+        <v>8400.0</v>
       </c>
       <c r="G8" s="1">
-        <v>7200.0</v>
+        <v>7500.0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="1">
-        <v>18500.0</v>
+        <v>8600.0</v>
       </c>
       <c r="G9" s="1">
-        <v>17500.0</v>
+        <v>7600.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>61</v>
+      <c r="J9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1">
-        <v>4600.0</v>
+        <v>13300.0</v>
       </c>
       <c r="G10" s="1">
-        <v>4500.0</v>
+        <v>12800.0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>18</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1">
-        <v>4800.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G11" s="1">
-        <v>4600.0</v>
+        <v>7800.0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8800.0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8100.0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="1">
-        <v>4900.0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>4700.0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="1">
-        <v>5450.0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>4800.0</v>
+        <v>66</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8200.0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7500.0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F14" s="1">
-        <v>5800.0</v>
+        <v>7800.0</v>
       </c>
       <c r="G14" s="1">
-        <v>5300.0</v>
+        <v>7200.0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>19</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F15" s="1">
-        <v>8400.0</v>
+        <v>7300.0</v>
       </c>
       <c r="G15" s="1">
-        <v>7500.0</v>
+        <v>6800.0</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>93</v>
+        <v>67</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F16" s="1">
-        <v>13500.0</v>
+        <v>7100.0</v>
       </c>
       <c r="G16" s="1">
-        <v>12800.0</v>
+        <v>6700.0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>37</v>
+      <c r="K16" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>100</v>
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F17" s="1">
-        <v>37500.0</v>
+        <v>10200.0</v>
       </c>
       <c r="G17" s="1">
-        <v>36800.0</v>
+        <v>9500.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>105</v>
+        <v>67</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>87</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F18" s="1">
-        <v>24000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G18" s="1">
-        <v>23500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>110</v>
+        <v>67</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>113</v>
+      <c r="A19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="1">
-        <v>14175.0</v>
+        <v>66</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8800.0</v>
       </c>
       <c r="G19" s="1">
-        <v>13925.0</v>
+        <v>7500.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>118</v>
+        <v>67</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F20" s="1">
-        <v>31900.0</v>
+        <v>13500.0</v>
       </c>
       <c r="G20" s="1">
-        <v>30500.0</v>
+        <v>12800.0</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>110</v>
+        <v>67</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>124</v>
+      <c r="A21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F21" s="1">
-        <v>19900.0</v>
+        <v>8200.0</v>
       </c>
       <c r="G21" s="1">
-        <v>17800.0</v>
+        <v>7500.0</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+        <v>67</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="1" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>102</v>
@@ -2009,308 +2619,308 @@
         <v>103</v>
       </c>
       <c r="F22" s="1">
-        <v>30500.0</v>
+        <v>4600.0</v>
       </c>
       <c r="G22" s="1">
-        <v>29500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>131</v>
+        <v>105</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>135</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="1">
-        <v>5200.0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>4700.0</v>
+        <v>111</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4300.0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3800.0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+        <v>105</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>139</v>
+        <v>114</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="1">
-        <v>7200.0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>6800.0</v>
+        <v>111</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4400.0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3900.0</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>141</v>
+        <v>105</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F25" s="1">
-        <v>28900.0</v>
+        <v>4800.0</v>
       </c>
       <c r="G25" s="1">
-        <v>28000.0</v>
+        <v>4600.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>144</v>
+        <v>105</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F26" s="1">
-        <v>13500.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G26" s="1">
-        <v>12500.0</v>
+        <v>3200.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>92</v>
+      <c r="B27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="1">
-        <v>6800.0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>6400.0</v>
+        <v>127</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4700.0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4200.0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+        <v>129</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>3200.0</v>
+        <v>127</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5100.0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4200.0</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>157</v>
+        <v>129</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="F29" s="1">
-        <v>4200.0</v>
+        <v>4900.0</v>
       </c>
       <c r="G29" s="1">
-        <v>3800.0</v>
+        <v>4700.0</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="F30" s="1">
         <v>3600.0</v>
@@ -2322,606 +2932,620 @@
         <v>17</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>81</v>
+        <v>129</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>163</v>
+      <c r="A31" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="F31" s="1">
-        <v>8500.0</v>
+        <v>5900.0</v>
       </c>
       <c r="G31" s="1">
-        <v>7500.0</v>
+        <v>4900.0</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>37</v>
+        <v>145</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>92</v>
+        <v>148</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="1">
-        <v>8600.0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>7600.0</v>
+        <v>143</v>
+      </c>
+      <c r="F32" s="2">
+        <v>5500.0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>4700.0</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>168</v>
+        <v>145</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>92</v>
+      <c r="A33" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="1">
-        <v>7100.0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>6700.0</v>
+        <v>102</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="2">
+        <v>5500.0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4900.0</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="F34" s="1">
-        <v>13400.0</v>
+        <v>4200.0</v>
       </c>
       <c r="G34" s="1">
-        <v>12500.0</v>
+        <v>3800.0</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>175</v>
+        <v>145</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>92</v>
+      <c r="A35" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="1">
-        <v>24000.0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>23000.0</v>
+      <c r="E35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F35" s="2">
+        <v>7200.0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>6200.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>181</v>
+        <v>145</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>114</v>
+        <v>160</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="1">
-        <v>35000.0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>33800.0</v>
+      <c r="E36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" s="2">
+        <v>6100.0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5200.0</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>186</v>
+        <v>145</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>97</v>
+      <c r="A37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F37" s="1">
-        <v>5900.0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>4900.0</v>
+        <v>102</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" s="2">
+        <v>4600.0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3900.0</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>189</v>
+        <v>145</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="1">
-        <v>8300.0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>7800.0</v>
+        <v>102</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="2">
+        <v>5700.0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>4900.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>192</v>
+        <v>145</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>195</v>
+      <c r="A39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="1">
-        <v>15500.0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>14500.0</v>
+        <v>102</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="2">
+        <v>5800.0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5300.0</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+        <v>145</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="F40" s="1">
-        <v>13995.0</v>
+        <v>11200.0</v>
       </c>
       <c r="G40" s="1">
-        <v>13500.0</v>
+        <v>10800.0</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="7">
+        <v>4200.0</v>
+      </c>
+      <c r="G41" s="7">
+        <v>3800.0</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="1">
-        <v>20200.0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>19000.0</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+      <c r="I41" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
+    </row>
+    <row r="42">
       <c r="A42" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>209</v>
+        <v>177</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="F42" s="1">
-        <v>13300.0</v>
+        <v>7900.0</v>
       </c>
       <c r="G42" s="1">
-        <v>12800.0</v>
+        <v>6400.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>212</v>
+        <v>145</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>214</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="F43" s="1">
-        <v>75000.0</v>
+        <v>5450.0</v>
       </c>
       <c r="G43" s="1">
-        <v>67000.0</v>
+        <v>4800.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>180</v>
+        <v>145</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="1" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="F44" s="1">
-        <v>13000.0</v>
+        <v>5800.0</v>
       </c>
       <c r="G44" s="1">
-        <v>12500.0</v>
+        <v>5300.0</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>201</v>
+        <v>145</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>222</v>
+      <c r="A45" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="F45" s="1">
-        <v>8500.0</v>
+        <v>5200.0</v>
       </c>
       <c r="G45" s="1">
-        <v>7800.0</v>
+        <v>4700.0</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>41</v>
+        <v>145</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>14</v>
+        <v>191</v>
+      </c>
+      <c r="C46" s="2">
+        <v>91.0</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="F46" s="1">
-        <v>7300.0</v>
+        <v>7200.0</v>
       </c>
       <c r="G46" s="1">
         <v>6800.0</v>
@@ -2930,77 +3554,91 @@
         <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="1">
-        <v>8200.0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>7500.0</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="A47" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F47" s="7">
+        <v>73000.0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>65000.0</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6"/>
+      <c r="T47" s="6"/>
+      <c r="U47" s="6"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="6"/>
+      <c r="X47" s="6"/>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>232</v>
+        <v>200</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="F48" s="1">
-        <v>13100.0</v>
+        <v>31000.0</v>
       </c>
       <c r="G48" s="1">
-        <v>12800.0</v>
+        <v>28000.0</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>17</v>
@@ -3009,74 +3647,74 @@
         <v>18</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>235</v>
+      <c r="A49" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="F49" s="1">
-        <v>73000.0</v>
+        <v>75000.0</v>
       </c>
       <c r="G49" s="1">
-        <v>65000.0</v>
+        <v>67000.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>180</v>
+        <v>208</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="F50" s="1">
-        <v>24000.0</v>
+        <v>35000.0</v>
       </c>
       <c r="G50" s="1">
-        <v>23000.0</v>
+        <v>33800.0</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>17</v>
@@ -3085,74 +3723,74 @@
         <v>18</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1" t="s">
-        <v>243</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="F51" s="1">
-        <v>15900.0</v>
+        <v>37500.0</v>
       </c>
       <c r="G51" s="1">
-        <v>14900.0</v>
+        <v>36800.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>245</v>
+        <v>220</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>249</v>
+        <v>39</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F52" s="1">
-        <v>31000.0</v>
+        <v>24000.0</v>
       </c>
       <c r="G52" s="1">
-        <v>28000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>17</v>
@@ -3161,256 +3799,833 @@
         <v>18</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>251</v>
+        <v>225</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>65</v>
+      <c r="A53" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F53" s="1">
+        <v>28900.0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>28000.0</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" s="3">
-        <v>7200.0</v>
-      </c>
-      <c r="G53" s="3">
-        <v>6200.0</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I53" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>255</v>
+        <v>230</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>65</v>
+        <v>233</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F54" s="3">
-        <v>6100.0</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5200.0</v>
+        <v>196</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" s="1">
+        <v>30500.0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>29500.0</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L54" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>65</v>
+        <v>235</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" s="3">
-        <v>4600.0</v>
-      </c>
-      <c r="G55" s="3">
-        <v>3900.0</v>
+        <v>196</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="2">
+        <v>38000.0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>33000.0</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
+        <v>18</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>65</v>
+        <v>243</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="1">
+        <v>24000.0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>23500.0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" s="3">
-        <v>5700.0</v>
-      </c>
-      <c r="G56" s="3">
-        <v>4900.0</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I56" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>65</v>
+        <v>245</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" s="3">
-        <v>5800.0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5300.0</v>
+        <v>196</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="1">
+        <v>31900.0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>30500.0</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L57" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" s="7">
+        <v>24000.0</v>
+      </c>
+      <c r="G58" s="7">
+        <v>23000.0</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+      <c r="X58" s="6"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F59" s="1">
+        <v>20200.0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>19000.0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="7">
+        <v>18500.0</v>
+      </c>
+      <c r="G60" s="7">
+        <v>17500.0</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="K60" s="8" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
+      <c r="L60" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+      <c r="X60" s="6"/>
+      <c r="Y60" s="6"/>
+      <c r="Z60" s="6"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="9">
+        <v>19800.0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>16500.0</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="6"/>
+      <c r="Y61" s="6"/>
+      <c r="Z61" s="6"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="7">
+        <v>15500.0</v>
+      </c>
+      <c r="G62" s="7">
+        <v>14500.0</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+      <c r="X62" s="6"/>
+      <c r="Y62" s="6"/>
+      <c r="Z62" s="6"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F63" s="1">
+        <v>19900.0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>17800.0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="1">
+        <v>13400.0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>12500.0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="1">
+        <v>13500.0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>12500.0</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F66" s="7">
+        <v>13000.0</v>
+      </c>
+      <c r="G66" s="7">
+        <v>12500.0</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="6"/>
+      <c r="Y66" s="6"/>
+      <c r="Z66" s="6"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F67" s="7">
+        <v>13100.0</v>
+      </c>
+      <c r="G67" s="7">
+        <v>12800.0</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="6"/>
+      <c r="Z67" s="6"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F68" s="1">
+        <v>13995.0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>13500.0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F69" s="1">
+        <v>14175.0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>13925.0</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F70" s="7">
+        <v>15900.0</v>
+      </c>
+      <c r="G70" s="7">
+        <v>14900.0</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+      <c r="X70" s="6"/>
+      <c r="Y70" s="6"/>
+      <c r="Z70" s="6"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F71" s="2">
+        <v>17200.0</v>
+      </c>
+      <c r="G71" s="2">
+        <v>16200.0</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
     <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
     <row r="107" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1"/>
@@ -4305,15 +5520,54 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="L53"/>
-    <hyperlink r:id="rId2" ref="L54"/>
-    <hyperlink r:id="rId3" ref="L55"/>
-    <hyperlink r:id="rId4" ref="L56"/>
-    <hyperlink r:id="rId5" ref="L57"/>
+    <hyperlink r:id="rId1" ref="L3"/>
+    <hyperlink r:id="rId2" ref="L4"/>
+    <hyperlink r:id="rId3" ref="L13"/>
+    <hyperlink r:id="rId4" ref="L19"/>
+    <hyperlink r:id="rId5" ref="L21"/>
+    <hyperlink r:id="rId6" ref="L23"/>
+    <hyperlink r:id="rId7" ref="L24"/>
+    <hyperlink r:id="rId8" ref="L27"/>
+    <hyperlink r:id="rId9" ref="L28"/>
+    <hyperlink r:id="rId10" ref="L32"/>
+    <hyperlink r:id="rId11" ref="L33"/>
+    <hyperlink r:id="rId12" ref="L35"/>
+    <hyperlink r:id="rId13" ref="L36"/>
+    <hyperlink r:id="rId14" ref="L37"/>
+    <hyperlink r:id="rId15" ref="L38"/>
+    <hyperlink r:id="rId16" ref="L39"/>
+    <hyperlink r:id="rId17" ref="L55"/>
+    <hyperlink r:id="rId18" ref="L61"/>
   </hyperlinks>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -4334,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -4342,86 +5596,86 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>277</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>280</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>283</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>287</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/store_inventory_template.xlsx
+++ b/store_inventory_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="347">
   <si>
     <t>product_id</t>
   </si>
@@ -1214,7 +1214,7 @@
     <t>Wheel Size: 26 Inches | Frame Material: High-Tensile  Steel Frame | Brake System: Front &amp; Rear Mechanical Power Brakes | Gears / Speed: Multi-Speed Gear System | Front Suspension: Suspension Steel Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting | Tire Dimensions: 26 x 4.0 Inch Ultra-Wide All-Terrain Tread</t>
   </si>
   <si>
-    <t>/images/products/prod_052_1_105NvCgjVtXGtaeqUeDr858YjfsaNBmNa.jpg</t>
+    <t>/images/products/prod_052_1_105NvCgjVtXGtaeqUeDr858YjfsaNBmNa.jpg,images/products/prod_024_2.jpg,</t>
   </si>
   <si>
     <t>prod_059</t>
@@ -1349,19 +1349,31 @@
     <t>prod_065</t>
   </si>
   <si>
-    <t>RALEIGH NAVARRO ONE 29T SS</t>
+    <t>SUNCROSS TOSCANO (21 SPEED) ALLOY</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile Alloy  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: 21Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1h6UEG4cGPgSi-oYXiNYmzuQLxD_Y5p-Q/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>prod_066</t>
+  </si>
+  <si>
+    <t>RALEIGH AVALANCHE 27.5T</t>
   </si>
   <si>
     <t>Durable and stylish adult cycle engineered with Hi-Ten Steel with Internal Cable Routing Frame, Dual Mechanical Disc Brakes (Front &amp; Rear), and sleek geometry for daily commutes and fitness rides.</t>
   </si>
   <si>
-    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile  Steel Frame Frame | Brake System: Dual Mechanical Disc Brakes| Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension  Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
-  </si>
-  <si>
-    <t>/images/products/prod_056_1_1Ws3eOH-sOZouOZB14wePKR-eqO69kGwH.jpg</t>
-  </si>
-  <si>
-    <t>prod_066</t>
+    <t>Wheel Size: 27.5T Inches | Frame Material: High-Tensile  Steel Frame Frame | Brake System: Dual Mechanical Disc Brakes| Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension  Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vwrVwG-FmGwAcVKAPCRwA8A1OGRX6OvW/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>prod_067</t>
   </si>
   <si>
     <t>RALEIGH PHASE PRO 29T S/S</t>
@@ -1373,7 +1385,7 @@
     <t>/images/products/prod_062_1.jpg</t>
   </si>
   <si>
-    <t>prod_067</t>
+    <t>prod_068</t>
   </si>
   <si>
     <t>RALEIGH EXALT 29T SS</t>
@@ -1385,7 +1397,7 @@
     <t>/images/products/prod_049_1_17DZ0XXndgxQv-Za--OftlEZ4Jo9MLJLK.jpg,/images/products/prod_049_2_1qV2Wmetczbft1-kyA6E2yKZ-X_QJYHWM.jpg</t>
   </si>
   <si>
-    <t>prod_068</t>
+    <t>prod_069</t>
   </si>
   <si>
     <t>RALEIGH NAVARRO ONE 29T (D/Disc)</t>
@@ -1394,10 +1406,10 @@
     <t>Wheel Size: 29 Inches | Frame Material:High-Tensile  Steel Frame | | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
   </si>
   <si>
-    <t>/images/products/prod_024_1.jpg,/images/products/prod_024_2.jpg,/images/products/prod_024_3.jpg</t>
-  </si>
-  <si>
-    <t>prod_069</t>
+    <t>/images/products/prod_024_1.jpg,/images/products/prod_024_3.jpg</t>
+  </si>
+  <si>
+    <t>prod_070</t>
   </si>
   <si>
     <t>RALEIGH CAPTUS 29T FSDD SS</t>
@@ -1409,7 +1421,7 @@
     <t>/images/products/prod_050_1_168Y_oxmz0eUB7UldAykn2oXjREuOzDWJ.jpg,/images/products/prod_050_2_13OKzmHpJoh0_SJpkc89YiaGslaRe_ivZ.jpg</t>
   </si>
   <si>
-    <t>prod_070</t>
+    <t>prod_071</t>
   </si>
   <si>
     <t>LUCIFIRE P Pro 12 29T</t>
@@ -1419,6 +1431,70 @@
   </si>
   <si>
     <t>Durable and stylish adult cycle engineered with Lightweight Aircraft-Grade Alloy Frame, Front &amp; Rear Mechanical Disc Brakes, and sleek geometry for daily commutes and fitness rides.</t>
+  </si>
+  <si>
+    <t>Wheel Size: 29 Inches | Frame Material: High-Tensile Alloy  Steel Frame | Brake System: Dual Mechanical Disc Brakes (Front &amp; Rear) | Gears / Speed: Single Speed Direct Drive | Front Suspension: Front Telescopic Suspension Fork | Target Age Group: 15+ Years | Ideal Location: Urban Roads, Fitness Trails &amp; City Commuting</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/127LKOEq44jMf3WgQ2mXYjDrPtVDvqcEm/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1dYpBo_0kJConVPzMcXPBkYNr-maCmwAh/view?usp=sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>prod_072</t>
+  </si>
+  <si>
+    <t>LUCIFIRE Morpheus 29T</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1sTpQlE2fZZjItcmXNZQLDc1GeMYBO8qF/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/10orTYGKpp5M1GbLDJroOK3zVOm9DC5EZ/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/file/d/1bJmsmm8f3_GlmsgFBroHEsYtnGzF_Ewd/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>,https://drive.google.com/file/d/1bJmsmm8f3_GlmsgFBroHEsYtnGzF_Ewd/view?usp=sharing</t>
+    </r>
   </si>
   <si>
     <t>slug</t>
@@ -1485,7 +1561,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -1520,6 +1596,12 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1541,7 +1623,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1571,6 +1653,9 @@
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -4084,7 +4169,7 @@
       <c r="K59" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="L59" s="2" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4362,38 +4447,38 @@
       <c r="A66" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E66" s="6" t="s">
+      <c r="C66" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="F66" s="7">
-        <v>13000.0</v>
-      </c>
-      <c r="G66" s="7">
-        <v>12500.0</v>
+      <c r="F66" s="9">
+        <v>23000.0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>21000.0</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="6" t="s">
+      <c r="I66" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J66" s="8" t="s">
+      <c r="J66" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K66" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K66" s="8" t="s">
+      <c r="L66" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
@@ -4412,10 +4497,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>298</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>212</v>
@@ -4423,14 +4508,14 @@
       <c r="D67" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F67" s="7">
-        <v>13100.0</v>
-      </c>
-      <c r="G67" s="7">
-        <v>12800.0</v>
+      <c r="E67" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="9">
+        <v>15000.0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>13900.0</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>17</v>
@@ -4439,12 +4524,12 @@
         <v>18</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K67" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="L67" s="6" t="s">
+      <c r="L67" s="11" t="s">
         <v>301</v>
       </c>
       <c r="M67" s="6"/>
@@ -4462,45 +4547,59 @@
       <c r="Y67" s="6"/>
       <c r="Z67" s="6"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68">
       <c r="A68" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F68" s="1">
-        <v>13995.0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>13500.0</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="F68" s="7">
+        <v>13100.0</v>
+      </c>
+      <c r="G68" s="7">
+        <v>12800.0</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="6" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="K68" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K68" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="L68" s="6" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
+      <c r="X68" s="6"/>
+      <c r="Y68" s="6"/>
+      <c r="Z68" s="6"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>306</v>
       </c>
@@ -4517,19 +4616,19 @@
         <v>260</v>
       </c>
       <c r="F69" s="1">
-        <v>14175.0</v>
+        <v>13995.0</v>
       </c>
       <c r="G69" s="1">
-        <v>13925.0</v>
+        <v>13500.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>308</v>
@@ -4538,67 +4637,53 @@
         <v>309</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70">
       <c r="A70" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F70" s="7">
-        <v>15900.0</v>
-      </c>
-      <c r="G70" s="7">
-        <v>14900.0</v>
-      </c>
-      <c r="H70" s="6" t="s">
+      <c r="F70" s="1">
+        <v>14175.0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>13925.0</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I70" s="6" t="s">
+      <c r="I70" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="K70" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="K70" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="L70" s="6" t="s">
+      <c r="L70" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="6"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>316</v>
+      <c r="C71" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>34</v>
@@ -4606,27 +4691,119 @@
       <c r="E71" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="2">
-        <v>17200.0</v>
-      </c>
-      <c r="G71" s="2">
-        <v>16200.0</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>17</v>
+      <c r="F71" s="7">
+        <v>15900.0</v>
+      </c>
+      <c r="G71" s="7">
+        <v>14900.0</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>18</v>
       </c>
       <c r="J71" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="L71" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="K71" s="8" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+      <c r="T71" s="6"/>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6"/>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F72" s="2">
+        <v>17200.0</v>
+      </c>
+      <c r="G72" s="2">
+        <v>16200.0</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73" s="2">
+        <v>14800.0</v>
+      </c>
+      <c r="G73" s="2">
+        <v>13800.0</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1"/>
     <row r="110" ht="15.75" customHeight="1"/>
@@ -5546,6 +5723,7 @@
     <row r="1024" ht="15.75" customHeight="1"/>
     <row r="1025" ht="15.75" customHeight="1"/>
     <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>
@@ -5566,8 +5744,12 @@
     <hyperlink r:id="rId16" ref="L39"/>
     <hyperlink r:id="rId17" ref="L55"/>
     <hyperlink r:id="rId18" ref="L61"/>
+    <hyperlink r:id="rId19" ref="L66"/>
+    <hyperlink r:id="rId20" ref="L67"/>
+    <hyperlink r:id="rId21" ref="L72"/>
+    <hyperlink r:id="rId22" ref="L73"/>
   </hyperlinks>
-  <drawing r:id="rId19"/>
+  <drawing r:id="rId23"/>
 </worksheet>
 </file>
 
@@ -5588,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -5599,13 +5781,13 @@
         <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
@@ -5613,13 +5795,13 @@
         <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -5627,13 +5809,13 @@
         <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
@@ -5641,13 +5823,13 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
@@ -5655,27 +5837,27 @@
         <v>196</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
